--- a/data/ytd-budget.xlsx
+++ b/data/ytd-budget.xlsx
@@ -1070,7 +1070,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2cad3ce6-d7df-455d-9180-446e5d78f544}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551fcbe8-967d-4a12-b3db-590f41ef8508}">
   <dimension ref="A1:Q60"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -2138,16 +2138,16 @@
         <v>5000</v>
       </c>
       <c r="M20" s="7">
-        <v>1877.99</v>
+        <v>2517.21</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="5">
-        <v>3122.01</v>
+        <v>2482.79</v>
       </c>
       <c r="P20" s="7">
-        <v>37.60</v>
+        <v>50.30</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>20</v>
@@ -2297,16 +2297,16 @@
         <v>186358</v>
       </c>
       <c r="M23" s="7">
-        <v>114859.10</v>
+        <v>117684.65</v>
       </c>
       <c r="N23" s="7">
-        <v>51264.64</v>
+        <v>48902.14</v>
       </c>
       <c r="O23" s="5">
-        <v>20234.26</v>
+        <v>19771.21</v>
       </c>
       <c r="P23" s="7">
-        <v>89.10</v>
+        <v>89.40</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>20</v>
@@ -2403,16 +2403,16 @@
         <v>100606</v>
       </c>
       <c r="M25" s="7">
-        <v>56011.38</v>
+        <v>56123.37</v>
       </c>
       <c r="N25" s="7">
         <v>10341</v>
       </c>
       <c r="O25" s="5">
-        <v>34253.62</v>
+        <v>34141.63</v>
       </c>
       <c r="P25" s="7">
-        <v>66</v>
+        <v>66.10</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>20</v>
@@ -2456,10 +2456,10 @@
         <v>146300</v>
       </c>
       <c r="M26" s="7">
-        <v>79892.21</v>
+        <v>84985.76</v>
       </c>
       <c r="N26" s="7">
-        <v>27190.19</v>
+        <v>22096.64</v>
       </c>
       <c r="O26" s="5">
         <v>39217.60</v>
@@ -2562,16 +2562,16 @@
         <v>235220</v>
       </c>
       <c r="M28" s="7">
-        <v>146170.33</v>
+        <v>148506.33</v>
       </c>
       <c r="N28" s="7">
         <v>127566.48</v>
       </c>
       <c r="O28" s="5">
-        <v>-38516.81</v>
+        <v>-40852.81</v>
       </c>
       <c r="P28" s="7">
-        <v>116.40</v>
+        <v>117.40</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>27</v>
@@ -3198,16 +3198,16 @@
         <v>360967</v>
       </c>
       <c r="M40" s="7">
-        <v>165352.03</v>
+        <v>167148.98</v>
       </c>
       <c r="N40" s="7">
         <v>12027.75</v>
       </c>
       <c r="O40" s="5">
-        <v>183587.22</v>
+        <v>181790.27</v>
       </c>
       <c r="P40" s="7">
-        <v>49.10</v>
+        <v>49.60</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>20</v>
@@ -3251,16 +3251,16 @@
         <v>45000</v>
       </c>
       <c r="M41" s="7">
-        <v>25201.90</v>
+        <v>33682.45</v>
       </c>
       <c r="N41" s="7">
-        <v>24539.88</v>
+        <v>18273.43</v>
       </c>
       <c r="O41" s="5">
-        <v>-4741.78</v>
+        <v>-6955.88</v>
       </c>
       <c r="P41" s="7">
-        <v>110.50</v>
+        <v>115.50</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>27</v>
@@ -3675,16 +3675,16 @@
         <v>215021</v>
       </c>
       <c r="M49" s="7">
-        <v>116910.73</v>
+        <v>117357.73</v>
       </c>
       <c r="N49" s="7">
-        <v>26112.11</v>
+        <v>27646.77</v>
       </c>
       <c r="O49" s="5">
-        <v>71998.16</v>
+        <v>70016.50</v>
       </c>
       <c r="P49" s="7">
-        <v>66.50</v>
+        <v>67.40</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>20</v>
@@ -3781,16 +3781,16 @@
         <v>197959</v>
       </c>
       <c r="M51" s="7">
-        <v>100354.04</v>
+        <v>148841.31</v>
       </c>
       <c r="N51" s="7">
         <v>0</v>
       </c>
       <c r="O51" s="5">
-        <v>97604.96</v>
+        <v>49117.69</v>
       </c>
       <c r="P51" s="7">
-        <v>50.70</v>
+        <v>75.20</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>20</v>
@@ -4046,16 +4046,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M56" s="7">
-        <v>12367610.470000001</v>
+        <v>12437828.550000001</v>
       </c>
       <c r="N56" s="7">
-        <v>412654.16</v>
+        <v>400466.32</v>
       </c>
       <c r="O56" s="5">
-        <v>2892834.14</v>
+        <v>2834803.90</v>
       </c>
       <c r="P56" s="7">
-        <v>81.50</v>
+        <v>81.90</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>27</v>
@@ -4099,16 +4099,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M57" s="7">
-        <v>12367610.470000001</v>
+        <v>12437828.550000001</v>
       </c>
       <c r="N57" s="7">
-        <v>412654.16</v>
+        <v>400466.32</v>
       </c>
       <c r="O57" s="5">
-        <v>2892834.14</v>
+        <v>2834803.90</v>
       </c>
       <c r="P57" s="7">
-        <v>81.50</v>
+        <v>81.90</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>27</v>
@@ -4205,16 +4205,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M59" s="7">
-        <v>12367610.470000001</v>
+        <v>12437828.550000001</v>
       </c>
       <c r="N59" s="7">
-        <v>412654.16</v>
+        <v>400466.32</v>
       </c>
       <c r="O59" s="5">
-        <v>2892834.14</v>
+        <v>2834803.90</v>
       </c>
       <c r="P59" s="7">
-        <v>81.50</v>
+        <v>81.90</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>27</v>
@@ -4258,16 +4258,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M60" s="7">
-        <v>12367610.470000001</v>
+        <v>12437828.550000001</v>
       </c>
       <c r="N60" s="7">
-        <v>412654.16</v>
+        <v>400466.32</v>
       </c>
       <c r="O60" s="5">
-        <v>2892834.14</v>
+        <v>2834803.90</v>
       </c>
       <c r="P60" s="7">
-        <v>81.50</v>
+        <v>81.90</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>27</v>
